--- a/public/templates/tsmc_vehicle_template.xlsx
+++ b/public/templates/tsmc_vehicle_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meanie\Documents\WebApp\TSMC\tsmc_web\public\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meanie\Documents\WebApp\TSMC\tsmc_web\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF13953A-C4BE-44D4-88E6-19DEF0F20588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEF0DAD-7EFE-4CB4-A04F-2E7929900988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E514ADE8-FAF0-4AF9-BC87-1C93E5D86F6D}"/>
+    <workbookView xWindow="5130" yWindow="1140" windowWidth="19170" windowHeight="12105" xr2:uid="{E514ADE8-FAF0-4AF9-BC87-1C93E5D86F6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>หมวดทะเบียนรถ</t>
   </si>
@@ -52,13 +52,61 @@
   </si>
   <si>
     <t>ประเภทประกันภัย</t>
+  </si>
+  <si>
+    <t>ลักษณะ/มาตรฐาน ต้องเป็นตามนี้เท่านั้น</t>
+  </si>
+  <si>
+    <t>รถกระบะบรรทุก</t>
+  </si>
+  <si>
+    <t>รถตู้บรรทุก</t>
+  </si>
+  <si>
+    <t>รถบรรทุกของเหลว</t>
+  </si>
+  <si>
+    <t>รถบรรทุกวัสดุอันตราย</t>
+  </si>
+  <si>
+    <t>รถบรรทุกเฉพาะกิจ</t>
+  </si>
+  <si>
+    <t>รถพ่วง</t>
+  </si>
+  <si>
+    <t>รถกึ่งพ่วง</t>
+  </si>
+  <si>
+    <t>รถกึ่งพ่วงบรรทุกวัสดุยาว</t>
+  </si>
+  <si>
+    <t>รถลากจูง</t>
+  </si>
+  <si>
+    <t>รถปรับอากาศพิเศษ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> รถปรับอากาศ</t>
+  </si>
+  <si>
+    <t>รถที่ไม่มีเครื่องปรับอากาศ</t>
+  </si>
+  <si>
+    <t>รถสองชั้น</t>
+  </si>
+  <si>
+    <t> รถกึ่งพ่วง</t>
+  </si>
+  <si>
+    <t>รถโดยสารเฉพาะกิจ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,16 +121,43 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Angsana New"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -90,16 +165,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ 2" xfId="1" xr:uid="{AA6EA12A-7FB1-4377-9105-8DF64C4D869D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -411,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68454CA-016D-4467-9685-4279A866AC2C}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -421,9 +521,11 @@
     <col min="6" max="6" width="13.140625" customWidth="1"/>
     <col min="8" max="8" width="11.5703125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" customWidth="1"/>
+    <col min="14" max="14" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -451,8 +553,83 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="M1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" ht="16.5">
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16.5">
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16.5">
+      <c r="M4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16.5">
+      <c r="M5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16.5">
+      <c r="M6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16.5">
+      <c r="M7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16.5">
+      <c r="M8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16.5">
+      <c r="M9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" ht="16.5">
+      <c r="M10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="M1:N1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
